--- a/docs/implementation-guide.xlsx
+++ b/docs/implementation-guide.xlsx
@@ -205,7 +205,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go の書き方入門 (./go-guide.md) / 基本設計書 (./basic-design.md) / テーブル定義書 (./table-definition.md)</t>
+          <t xml:space="preserve">Go の書き方入門 (./go-guide.md) / API 仕様書 (./api-spec.md) / 基本設計書 (./basic-design.md) / テーブル定義書 (./table-definition.md)</t>
         </is>
       </c>
     </row>
@@ -2511,19 +2511,33 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・設計書に手を入れる。この例なら基本設計書の「機能一覧」「API 設計」「制約事項 #3」が対象。</t>
+          <t xml:space="preserve">・API 仕様書 (./api-spec.md) を直す。 この例なら「7.1 PATCH /api/duties/{id}」を確定仕様として</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・md を直したら make docs で xlsx を作り直す。</t>
+          <t xml:space="preserve">「5. エンドポイント詳細」へ移し、エンドポイント一覧の状態を「確定」にする。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">・設計書に手を入れる。この例なら基本設計書の「機能一覧」「制約事項 #3」が対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">・md を直したら make docs で xlsx を作り直す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">・コミットする (「8. 複数人で進めるとき」を参照)。</t>
         </is>

--- a/docs/implementation-guide.xlsx
+++ b/docs/implementation-guide.xlsx
@@ -340,7 +340,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="46" customWidth="1"/>
   </cols>
@@ -596,7 +596,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl http://localhost:8080/api/employees</t>
+          <t xml:space="preserve">curl http://localhost:8080/api/people</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">当番データが入っている</t>
+          <t xml:space="preserve">抽選結果データが入っている</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl http://localhost:8080/api/duties</t>
+          <t xml:space="preserve">curl http://localhost:8080/api/lottery-results</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  │  http://localhost:8080/api/duties</t>
+          <t xml:space="preserve">  │  http://localhost:8080/api/lottery-results</t>
         </is>
       </c>
     </row>
@@ -1459,14 +1459,14 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">現状、当番の状態 (duties.status) を pending から変える手段が無い</t>
+          <t xml:space="preserve">現状、抽選結果の状態 (lottery_result.status) を pending から変える手段が無い</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(基本設計書の「制約事項 #3」)。これを解消する PATCH /api/duties/:id を追加する。</t>
+          <t xml:space="preserve">(基本設計書の「制約事項 #3」)。これを解消する PATCH /api/lottery-results/:id を追加する。</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATCH /api/duties/:id</t>
+          <t xml:space="preserve">PATCH /api/lottery-results/:id</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl -X PATCH http://localhost:8080/api/duties/1 \</t>
+          <t xml:space="preserve">curl -X PATCH http://localhost:8080/api/lottery-results/1 \</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl -s http://localhost:8080/api/duties | head -c 300</t>
+          <t xml:space="preserve">curl -s http://localhost:8080/api/lottery-results | head -c 300</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl -i -X PATCH http://localhost:8080/api/duties/99999 \</t>
+          <t xml:space="preserve">curl -i -X PATCH http://localhost:8080/api/lottery-results/99999 \</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl -i -X PATCH http://localhost:8080/api/duties/1 \</t>
+          <t xml:space="preserve">curl -i -X PATCH http://localhost:8080/api/lottery-results/1 \</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    await fetch(`/api/duties/${id}`, {</t>
+          <t xml:space="preserve">    await fetch(`/api/lottery-results/${id}`, {</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">・API 仕様書 (./api-spec.md) を直す。 この例なら「7.1 PATCH /api/duties/{id}」を確定仕様として</t>
+          <t xml:space="preserve">・API 仕様書 (./api-spec.md) を直す。 この例なら「7.1 PATCH /api/lottery-results/{id}」を確定仕様として</t>
         </is>
       </c>
     </row>
@@ -2578,28 +2578,28 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl http://localhost:8080/api/employees</t>
+          <t xml:space="preserve">curl http://localhost:8080/api/people</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl http://localhost:8080/api/areas</t>
+          <t xml:space="preserve">curl http://localhost:8080/api/tasks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl http://localhost:8080/api/duties</t>
+          <t xml:space="preserve">curl http://localhost:8080/api/lottery-results</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">curl -X POST http://localhost:8080/api/duties/generate</t>
+          <t xml:space="preserve">curl -X POST http://localhost:8080/api/lottery-results/generate</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gin のログには [GIN] ... | 200 | ... | PATCH /api/duties/1 のようにステータスとパスが出る。</t>
+          <t xml:space="preserve">Gin のログには [GIN] ... | 200 | ... | PATCH /api/lottery-results/1 のようにステータスとパスが出る。</t>
         </is>
       </c>
     </row>
